--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2020.xlsx
@@ -15589,7 +15589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población matriculada</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2020.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2020.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:38</t>
+    <t xml:space="preserve">2026-09-07 12:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2020.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:56</t>
+    <t xml:space="preserve">2026-09-08 10:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
